--- a/Module_4_Applied_Biostatistics/Data/Coloc_Example.xlsx
+++ b/Module_4_Applied_Biostatistics/Data/Coloc_Example.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sven\Desktop\Bioinformatik\ABI-2026-2\Module_4_Applied_Biostatistics\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F29009-A970-41E8-8B3E-366ADADA9AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABA44C7-F0EC-43AE-8858-A25463A8E13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0D67E6D3-F4DA-442B-B9DB-6DE0AB488676}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{0D67E6D3-F4DA-442B-B9DB-6DE0AB488676}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Timeseries" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="8">
   <si>
     <t>Strain</t>
   </si>
@@ -53,13 +54,16 @@
     <t>WT</t>
   </si>
   <si>
-    <t>Mut</t>
-  </si>
-  <si>
     <t>Replicate</t>
   </si>
   <si>
     <t>Mut2</t>
+  </si>
+  <si>
+    <t>Mut1</t>
+  </si>
+  <si>
+    <t>Time [min]</t>
   </si>
 </sst>
 </file>
@@ -437,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35A8A19A-3DED-438C-97C1-A45C22CF7CE5}">
-  <dimension ref="A1:D147"/>
+  <dimension ref="A1:D167"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -445,7 +449,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -470,7 +474,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -484,7 +488,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -498,7 +502,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -512,7 +516,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>3</v>
@@ -526,7 +530,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -540,7 +544,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -554,7 +558,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -568,7 +572,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1366,7 +1370,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -1380,7 +1384,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -1394,7 +1398,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -1408,7 +1412,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -1422,7 +1426,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -1436,7 +1440,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -1450,7 +1454,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -1464,7 +1468,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -1478,7 +1482,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -1492,7 +1496,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -1506,7 +1510,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -1520,7 +1524,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B78">
         <v>1</v>
@@ -1534,7 +1538,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -1548,7 +1552,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -1562,7 +1566,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -1576,7 +1580,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -1590,7 +1594,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -1604,7 +1608,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B84">
         <v>1</v>
@@ -1618,7 +1622,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -1632,7 +1636,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -1646,7 +1650,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -1660,7 +1664,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -1674,7 +1678,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -1688,7 +1692,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -1702,7 +1706,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B91">
         <v>2</v>
@@ -1716,7 +1720,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -1730,7 +1734,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -1744,7 +1748,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B94">
         <v>2</v>
@@ -1758,7 +1762,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B95">
         <v>2</v>
@@ -1772,7 +1776,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B96">
         <v>2</v>
@@ -1786,7 +1790,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B97">
         <v>2</v>
@@ -1800,7 +1804,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B98">
         <v>2</v>
@@ -1814,7 +1818,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B99">
         <v>2</v>
@@ -1828,7 +1832,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B100">
         <v>2</v>
@@ -1842,7 +1846,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B101">
         <v>2</v>
@@ -1856,7 +1860,7 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B102">
         <v>2</v>
@@ -1870,7 +1874,7 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B103">
         <v>3</v>
@@ -1884,7 +1888,7 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B104">
         <v>3</v>
@@ -1898,7 +1902,7 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B105">
         <v>3</v>
@@ -1912,7 +1916,7 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B106">
         <v>3</v>
@@ -1926,7 +1930,7 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B107">
         <v>3</v>
@@ -1940,7 +1944,7 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B108">
         <v>3</v>
@@ -1954,7 +1958,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B109">
         <v>3</v>
@@ -1968,7 +1972,7 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B110">
         <v>3</v>
@@ -1982,7 +1986,7 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B111">
         <v>3</v>
@@ -1996,7 +2000,7 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B112">
         <v>3</v>
@@ -2010,7 +2014,7 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B113">
         <v>3</v>
@@ -2024,7 +2028,7 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -2038,7 +2042,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -2052,7 +2056,7 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -2066,7 +2070,7 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -2080,7 +2084,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -2094,7 +2098,7 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -2108,7 +2112,7 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B120">
         <v>2</v>
@@ -2122,7 +2126,7 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B121">
         <v>2</v>
@@ -2136,7 +2140,7 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B122">
         <v>2</v>
@@ -2150,7 +2154,7 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B123">
         <v>2</v>
@@ -2164,7 +2168,7 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B124">
         <v>2</v>
@@ -2178,7 +2182,7 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B125">
         <v>2</v>
@@ -2192,7 +2196,7 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B126">
         <v>2</v>
@@ -2206,7 +2210,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B127">
         <v>2</v>
@@ -2220,7 +2224,7 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B128">
         <v>3</v>
@@ -2234,7 +2238,7 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B129">
         <v>3</v>
@@ -2248,7 +2252,7 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B130">
         <v>3</v>
@@ -2262,7 +2266,7 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B131">
         <v>3</v>
@@ -2276,7 +2280,7 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B132">
         <v>3</v>
@@ -2290,7 +2294,7 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B133">
         <v>3</v>
@@ -2304,7 +2308,7 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B134">
         <v>3</v>
@@ -2318,7 +2322,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B135">
         <v>3</v>
@@ -2332,7 +2336,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B136">
         <v>3</v>
@@ -2346,44 +2350,44 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B137">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C137">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D137">
-        <v>0.85</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B138">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C138">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D138">
-        <v>0.86</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B139">
+        <v>1</v>
+      </c>
+      <c r="C139">
         <v>4</v>
       </c>
-      <c r="C139">
-        <v>12</v>
-      </c>
       <c r="D139">
-        <v>0.95</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
@@ -2394,10 +2398,10 @@
         <v>1</v>
       </c>
       <c r="C140">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D140">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
@@ -2408,10 +2412,10 @@
         <v>1</v>
       </c>
       <c r="C141">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D141">
-        <v>0.02</v>
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
@@ -2422,10 +2426,10 @@
         <v>1</v>
       </c>
       <c r="C142">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D142">
-        <v>0.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
@@ -2436,10 +2440,10 @@
         <v>1</v>
       </c>
       <c r="C143">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D143">
-        <v>0.11</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
@@ -2450,56 +2454,2744 @@
         <v>1</v>
       </c>
       <c r="C144">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D144">
-        <v>0.14000000000000001</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C145">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C146">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D146">
-        <v>0.31</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C147">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D147">
-        <v>0.24</v>
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>5</v>
+      </c>
+      <c r="B148">
+        <v>2</v>
+      </c>
+      <c r="C148">
+        <v>13</v>
+      </c>
+      <c r="D148">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>5</v>
+      </c>
+      <c r="B149">
+        <v>2</v>
+      </c>
+      <c r="C149">
+        <v>14</v>
+      </c>
+      <c r="D149">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>5</v>
+      </c>
+      <c r="B150">
+        <v>2</v>
+      </c>
+      <c r="C150">
+        <v>15</v>
+      </c>
+      <c r="D150">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>5</v>
+      </c>
+      <c r="B151">
+        <v>2</v>
+      </c>
+      <c r="C151">
+        <v>16</v>
+      </c>
+      <c r="D151">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>5</v>
+      </c>
+      <c r="B152">
+        <v>2</v>
+      </c>
+      <c r="C152">
+        <v>17</v>
+      </c>
+      <c r="D152">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>5</v>
+      </c>
+      <c r="B153">
+        <v>2</v>
+      </c>
+      <c r="C153">
+        <v>18</v>
+      </c>
+      <c r="D153">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>5</v>
+      </c>
+      <c r="B154">
+        <v>2</v>
+      </c>
+      <c r="C154">
+        <v>19</v>
+      </c>
+      <c r="D154">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>5</v>
+      </c>
+      <c r="B155">
+        <v>2</v>
+      </c>
+      <c r="C155">
+        <v>20</v>
+      </c>
+      <c r="D155">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>5</v>
+      </c>
+      <c r="B156">
+        <v>3</v>
+      </c>
+      <c r="C156">
+        <v>10</v>
+      </c>
+      <c r="D156">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>5</v>
+      </c>
+      <c r="B157">
+        <v>3</v>
+      </c>
+      <c r="C157">
+        <v>11</v>
+      </c>
+      <c r="D157">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>5</v>
+      </c>
+      <c r="B158">
+        <v>3</v>
+      </c>
+      <c r="C158">
+        <v>12</v>
+      </c>
+      <c r="D158">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>5</v>
+      </c>
+      <c r="B159">
+        <v>3</v>
+      </c>
+      <c r="C159">
+        <v>13</v>
+      </c>
+      <c r="D159">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>5</v>
+      </c>
+      <c r="B160">
+        <v>3</v>
+      </c>
+      <c r="C160">
+        <v>14</v>
+      </c>
+      <c r="D160">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>5</v>
+      </c>
+      <c r="B161">
+        <v>3</v>
+      </c>
+      <c r="C161">
+        <v>15</v>
+      </c>
+      <c r="D161">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>5</v>
+      </c>
+      <c r="B162">
+        <v>3</v>
+      </c>
+      <c r="C162">
+        <v>16</v>
+      </c>
+      <c r="D162">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>5</v>
+      </c>
+      <c r="B163">
+        <v>3</v>
+      </c>
+      <c r="C163">
+        <v>17</v>
+      </c>
+      <c r="D163">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>5</v>
+      </c>
+      <c r="B164">
+        <v>3</v>
+      </c>
+      <c r="C164">
+        <v>18</v>
+      </c>
+      <c r="D164">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>5</v>
+      </c>
+      <c r="B165">
+        <v>3</v>
+      </c>
+      <c r="C165">
+        <v>19</v>
+      </c>
+      <c r="D165">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>5</v>
+      </c>
+      <c r="B166">
+        <v>3</v>
+      </c>
+      <c r="C166">
+        <v>20</v>
+      </c>
+      <c r="D166">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>5</v>
+      </c>
+      <c r="B167">
+        <v>3</v>
+      </c>
+      <c r="C167">
+        <v>21</v>
+      </c>
+      <c r="D167">
+        <v>0.96</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FB7305D-EE15-4FE3-8866-A06D105216EA}">
+  <dimension ref="A1:E141"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
+      </c>
+      <c r="E13">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="E14">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
+      </c>
+      <c r="D15">
+        <v>10</v>
+      </c>
+      <c r="E15">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16">
+        <v>10</v>
+      </c>
+      <c r="E16">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>15</v>
+      </c>
+      <c r="E17">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>15</v>
+      </c>
+      <c r="E18">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>15</v>
+      </c>
+      <c r="E19">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <v>15</v>
+      </c>
+      <c r="E20">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>5</v>
+      </c>
+      <c r="D21">
+        <v>15</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>20</v>
+      </c>
+      <c r="E22">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>20</v>
+      </c>
+      <c r="E23">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24">
+        <v>20</v>
+      </c>
+      <c r="E24">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25">
+        <v>20</v>
+      </c>
+      <c r="E25">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26">
+        <v>20</v>
+      </c>
+      <c r="E26">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>25</v>
+      </c>
+      <c r="E27">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>25</v>
+      </c>
+      <c r="E28">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29">
+        <v>25</v>
+      </c>
+      <c r="E29">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>4</v>
+      </c>
+      <c r="D30">
+        <v>25</v>
+      </c>
+      <c r="E30">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>5</v>
+      </c>
+      <c r="D31">
+        <v>25</v>
+      </c>
+      <c r="E31">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>30</v>
+      </c>
+      <c r="E32">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>30</v>
+      </c>
+      <c r="E33">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34">
+        <v>30</v>
+      </c>
+      <c r="E34">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
+      <c r="D35">
+        <v>30</v>
+      </c>
+      <c r="E35">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36">
+        <v>5</v>
+      </c>
+      <c r="D36">
+        <v>30</v>
+      </c>
+      <c r="E36">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40">
+        <v>4</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41">
+        <v>5</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>5</v>
+      </c>
+      <c r="E42">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43">
+        <v>5</v>
+      </c>
+      <c r="E43">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
+      <c r="D44">
+        <v>5</v>
+      </c>
+      <c r="E44">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>4</v>
+      </c>
+      <c r="D45">
+        <v>5</v>
+      </c>
+      <c r="E45">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>5</v>
+      </c>
+      <c r="D46">
+        <v>5</v>
+      </c>
+      <c r="E46">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>10</v>
+      </c>
+      <c r="E47">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48">
+        <v>10</v>
+      </c>
+      <c r="E48">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49">
+        <v>3</v>
+      </c>
+      <c r="D49">
+        <v>10</v>
+      </c>
+      <c r="E49">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <v>4</v>
+      </c>
+      <c r="D50">
+        <v>10</v>
+      </c>
+      <c r="E50">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51">
+        <v>5</v>
+      </c>
+      <c r="D51">
+        <v>10</v>
+      </c>
+      <c r="E51">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>15</v>
+      </c>
+      <c r="E52">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53">
+        <v>15</v>
+      </c>
+      <c r="E53">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <v>3</v>
+      </c>
+      <c r="D54">
+        <v>15</v>
+      </c>
+      <c r="E54">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55">
+        <v>4</v>
+      </c>
+      <c r="D55">
+        <v>15</v>
+      </c>
+      <c r="E55">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56">
+        <v>5</v>
+      </c>
+      <c r="D56">
+        <v>15</v>
+      </c>
+      <c r="E56">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>20</v>
+      </c>
+      <c r="E57">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+      <c r="D58">
+        <v>20</v>
+      </c>
+      <c r="E58">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59">
+        <v>3</v>
+      </c>
+      <c r="D59">
+        <v>20</v>
+      </c>
+      <c r="E59">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60">
+        <v>4</v>
+      </c>
+      <c r="D60">
+        <v>20</v>
+      </c>
+      <c r="E60">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61">
+        <v>5</v>
+      </c>
+      <c r="D61">
+        <v>20</v>
+      </c>
+      <c r="E61">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>25</v>
+      </c>
+      <c r="E62">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63">
+        <v>25</v>
+      </c>
+      <c r="E63">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>6</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64">
+        <v>25</v>
+      </c>
+      <c r="E64">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+      <c r="C65">
+        <v>4</v>
+      </c>
+      <c r="D65">
+        <v>25</v>
+      </c>
+      <c r="E65">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>6</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66">
+        <v>5</v>
+      </c>
+      <c r="D66">
+        <v>25</v>
+      </c>
+      <c r="E66">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>6</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+      <c r="D67">
+        <v>30</v>
+      </c>
+      <c r="E67">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>6</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68">
+        <v>2</v>
+      </c>
+      <c r="D68">
+        <v>30</v>
+      </c>
+      <c r="E68">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="C69">
+        <v>3</v>
+      </c>
+      <c r="D69">
+        <v>30</v>
+      </c>
+      <c r="E69">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>6</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70">
+        <v>4</v>
+      </c>
+      <c r="D70">
+        <v>30</v>
+      </c>
+      <c r="E70">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>6</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
+      <c r="C71">
+        <v>5</v>
+      </c>
+      <c r="D71">
+        <v>30</v>
+      </c>
+      <c r="E71">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73">
+        <v>2</v>
+      </c>
+      <c r="C73">
+        <v>2</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74">
+        <v>2</v>
+      </c>
+      <c r="C74">
+        <v>3</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75">
+        <v>2</v>
+      </c>
+      <c r="C75">
+        <v>4</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76">
+        <v>2</v>
+      </c>
+      <c r="C76">
+        <v>5</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77">
+        <v>2</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77">
+        <v>5</v>
+      </c>
+      <c r="E77">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
+      </c>
+      <c r="C78">
+        <v>2</v>
+      </c>
+      <c r="D78">
+        <v>5</v>
+      </c>
+      <c r="E78">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+      <c r="C79">
+        <v>3</v>
+      </c>
+      <c r="D79">
+        <v>5</v>
+      </c>
+      <c r="E79">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>3</v>
+      </c>
+      <c r="B80">
+        <v>2</v>
+      </c>
+      <c r="C80">
+        <v>4</v>
+      </c>
+      <c r="D80">
+        <v>5</v>
+      </c>
+      <c r="E80">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81">
+        <v>2</v>
+      </c>
+      <c r="C81">
+        <v>5</v>
+      </c>
+      <c r="D81">
+        <v>5</v>
+      </c>
+      <c r="E81">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82">
+        <v>2</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82">
+        <v>10</v>
+      </c>
+      <c r="E82">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83">
+        <v>2</v>
+      </c>
+      <c r="C83">
+        <v>2</v>
+      </c>
+      <c r="D83">
+        <v>10</v>
+      </c>
+      <c r="E83">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>3</v>
+      </c>
+      <c r="B84">
+        <v>2</v>
+      </c>
+      <c r="C84">
+        <v>3</v>
+      </c>
+      <c r="D84">
+        <v>10</v>
+      </c>
+      <c r="E84">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85">
+        <v>2</v>
+      </c>
+      <c r="C85">
+        <v>4</v>
+      </c>
+      <c r="D85">
+        <v>10</v>
+      </c>
+      <c r="E85">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86">
+        <v>2</v>
+      </c>
+      <c r="C86">
+        <v>5</v>
+      </c>
+      <c r="D86">
+        <v>10</v>
+      </c>
+      <c r="E86">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87">
+        <v>2</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+      <c r="D87">
+        <v>15</v>
+      </c>
+      <c r="E87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>3</v>
+      </c>
+      <c r="B88">
+        <v>2</v>
+      </c>
+      <c r="C88">
+        <v>2</v>
+      </c>
+      <c r="D88">
+        <v>15</v>
+      </c>
+      <c r="E88">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>3</v>
+      </c>
+      <c r="B89">
+        <v>2</v>
+      </c>
+      <c r="C89">
+        <v>3</v>
+      </c>
+      <c r="D89">
+        <v>15</v>
+      </c>
+      <c r="E89">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90">
+        <v>2</v>
+      </c>
+      <c r="C90">
+        <v>4</v>
+      </c>
+      <c r="D90">
+        <v>15</v>
+      </c>
+      <c r="E90">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91">
+        <v>2</v>
+      </c>
+      <c r="C91">
+        <v>5</v>
+      </c>
+      <c r="D91">
+        <v>15</v>
+      </c>
+      <c r="E91">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>3</v>
+      </c>
+      <c r="B92">
+        <v>2</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92">
+        <v>20</v>
+      </c>
+      <c r="E92">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>3</v>
+      </c>
+      <c r="B93">
+        <v>2</v>
+      </c>
+      <c r="C93">
+        <v>2</v>
+      </c>
+      <c r="D93">
+        <v>20</v>
+      </c>
+      <c r="E93">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>3</v>
+      </c>
+      <c r="B94">
+        <v>2</v>
+      </c>
+      <c r="C94">
+        <v>3</v>
+      </c>
+      <c r="D94">
+        <v>20</v>
+      </c>
+      <c r="E94">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>3</v>
+      </c>
+      <c r="B95">
+        <v>2</v>
+      </c>
+      <c r="C95">
+        <v>4</v>
+      </c>
+      <c r="D95">
+        <v>20</v>
+      </c>
+      <c r="E95">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>3</v>
+      </c>
+      <c r="B96">
+        <v>2</v>
+      </c>
+      <c r="C96">
+        <v>5</v>
+      </c>
+      <c r="D96">
+        <v>20</v>
+      </c>
+      <c r="E96">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>3</v>
+      </c>
+      <c r="B97">
+        <v>2</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97">
+        <v>25</v>
+      </c>
+      <c r="E97">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98">
+        <v>2</v>
+      </c>
+      <c r="C98">
+        <v>2</v>
+      </c>
+      <c r="D98">
+        <v>25</v>
+      </c>
+      <c r="E98">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>3</v>
+      </c>
+      <c r="B99">
+        <v>2</v>
+      </c>
+      <c r="C99">
+        <v>3</v>
+      </c>
+      <c r="D99">
+        <v>25</v>
+      </c>
+      <c r="E99">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100">
+        <v>2</v>
+      </c>
+      <c r="C100">
+        <v>4</v>
+      </c>
+      <c r="D100">
+        <v>25</v>
+      </c>
+      <c r="E100">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>3</v>
+      </c>
+      <c r="B101">
+        <v>2</v>
+      </c>
+      <c r="C101">
+        <v>5</v>
+      </c>
+      <c r="D101">
+        <v>25</v>
+      </c>
+      <c r="E101">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>3</v>
+      </c>
+      <c r="B102">
+        <v>2</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+      <c r="D102">
+        <v>30</v>
+      </c>
+      <c r="E102">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>3</v>
+      </c>
+      <c r="B103">
+        <v>2</v>
+      </c>
+      <c r="C103">
+        <v>2</v>
+      </c>
+      <c r="D103">
+        <v>30</v>
+      </c>
+      <c r="E103">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>3</v>
+      </c>
+      <c r="B104">
+        <v>2</v>
+      </c>
+      <c r="C104">
+        <v>3</v>
+      </c>
+      <c r="D104">
+        <v>30</v>
+      </c>
+      <c r="E104">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>3</v>
+      </c>
+      <c r="B105">
+        <v>2</v>
+      </c>
+      <c r="C105">
+        <v>4</v>
+      </c>
+      <c r="D105">
+        <v>30</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>3</v>
+      </c>
+      <c r="B106">
+        <v>2</v>
+      </c>
+      <c r="C106">
+        <v>5</v>
+      </c>
+      <c r="D106">
+        <v>30</v>
+      </c>
+      <c r="E106">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>6</v>
+      </c>
+      <c r="B107">
+        <v>2</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>6</v>
+      </c>
+      <c r="B108">
+        <v>2</v>
+      </c>
+      <c r="C108">
+        <v>2</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>6</v>
+      </c>
+      <c r="B109">
+        <v>2</v>
+      </c>
+      <c r="C109">
+        <v>3</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="E109">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>6</v>
+      </c>
+      <c r="B110">
+        <v>2</v>
+      </c>
+      <c r="C110">
+        <v>4</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>6</v>
+      </c>
+      <c r="B111">
+        <v>2</v>
+      </c>
+      <c r="C111">
+        <v>5</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112">
+        <v>2</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+      <c r="D112">
+        <v>5</v>
+      </c>
+      <c r="E112">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>6</v>
+      </c>
+      <c r="B113">
+        <v>2</v>
+      </c>
+      <c r="C113">
+        <v>2</v>
+      </c>
+      <c r="D113">
+        <v>5</v>
+      </c>
+      <c r="E113">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>6</v>
+      </c>
+      <c r="B114">
+        <v>2</v>
+      </c>
+      <c r="C114">
+        <v>3</v>
+      </c>
+      <c r="D114">
+        <v>5</v>
+      </c>
+      <c r="E114">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>6</v>
+      </c>
+      <c r="B115">
+        <v>2</v>
+      </c>
+      <c r="C115">
+        <v>4</v>
+      </c>
+      <c r="D115">
+        <v>5</v>
+      </c>
+      <c r="E115">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>6</v>
+      </c>
+      <c r="B116">
+        <v>2</v>
+      </c>
+      <c r="C116">
+        <v>5</v>
+      </c>
+      <c r="D116">
+        <v>5</v>
+      </c>
+      <c r="E116">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>6</v>
+      </c>
+      <c r="B117">
+        <v>2</v>
+      </c>
+      <c r="C117">
+        <v>1</v>
+      </c>
+      <c r="D117">
+        <v>10</v>
+      </c>
+      <c r="E117">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>6</v>
+      </c>
+      <c r="B118">
+        <v>2</v>
+      </c>
+      <c r="C118">
+        <v>2</v>
+      </c>
+      <c r="D118">
+        <v>10</v>
+      </c>
+      <c r="E118">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>6</v>
+      </c>
+      <c r="B119">
+        <v>2</v>
+      </c>
+      <c r="C119">
+        <v>3</v>
+      </c>
+      <c r="D119">
+        <v>10</v>
+      </c>
+      <c r="E119">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>6</v>
+      </c>
+      <c r="B120">
+        <v>2</v>
+      </c>
+      <c r="C120">
+        <v>4</v>
+      </c>
+      <c r="D120">
+        <v>10</v>
+      </c>
+      <c r="E120">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>6</v>
+      </c>
+      <c r="B121">
+        <v>2</v>
+      </c>
+      <c r="C121">
+        <v>5</v>
+      </c>
+      <c r="D121">
+        <v>10</v>
+      </c>
+      <c r="E121">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>6</v>
+      </c>
+      <c r="B122">
+        <v>2</v>
+      </c>
+      <c r="C122">
+        <v>1</v>
+      </c>
+      <c r="D122">
+        <v>15</v>
+      </c>
+      <c r="E122">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>6</v>
+      </c>
+      <c r="B123">
+        <v>2</v>
+      </c>
+      <c r="C123">
+        <v>2</v>
+      </c>
+      <c r="D123">
+        <v>15</v>
+      </c>
+      <c r="E123">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>6</v>
+      </c>
+      <c r="B124">
+        <v>2</v>
+      </c>
+      <c r="C124">
+        <v>3</v>
+      </c>
+      <c r="D124">
+        <v>15</v>
+      </c>
+      <c r="E124">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>6</v>
+      </c>
+      <c r="B125">
+        <v>2</v>
+      </c>
+      <c r="C125">
+        <v>4</v>
+      </c>
+      <c r="D125">
+        <v>15</v>
+      </c>
+      <c r="E125">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>6</v>
+      </c>
+      <c r="B126">
+        <v>2</v>
+      </c>
+      <c r="C126">
+        <v>5</v>
+      </c>
+      <c r="D126">
+        <v>15</v>
+      </c>
+      <c r="E126">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>6</v>
+      </c>
+      <c r="B127">
+        <v>2</v>
+      </c>
+      <c r="C127">
+        <v>1</v>
+      </c>
+      <c r="D127">
+        <v>20</v>
+      </c>
+      <c r="E127">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>6</v>
+      </c>
+      <c r="B128">
+        <v>2</v>
+      </c>
+      <c r="C128">
+        <v>2</v>
+      </c>
+      <c r="D128">
+        <v>20</v>
+      </c>
+      <c r="E128">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>6</v>
+      </c>
+      <c r="B129">
+        <v>2</v>
+      </c>
+      <c r="C129">
+        <v>3</v>
+      </c>
+      <c r="D129">
+        <v>20</v>
+      </c>
+      <c r="E129">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>6</v>
+      </c>
+      <c r="B130">
+        <v>2</v>
+      </c>
+      <c r="C130">
+        <v>4</v>
+      </c>
+      <c r="D130">
+        <v>20</v>
+      </c>
+      <c r="E130">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>6</v>
+      </c>
+      <c r="B131">
+        <v>2</v>
+      </c>
+      <c r="C131">
+        <v>5</v>
+      </c>
+      <c r="D131">
+        <v>20</v>
+      </c>
+      <c r="E131">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>6</v>
+      </c>
+      <c r="B132">
+        <v>2</v>
+      </c>
+      <c r="C132">
+        <v>1</v>
+      </c>
+      <c r="D132">
+        <v>25</v>
+      </c>
+      <c r="E132">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>6</v>
+      </c>
+      <c r="B133">
+        <v>2</v>
+      </c>
+      <c r="C133">
+        <v>2</v>
+      </c>
+      <c r="D133">
+        <v>25</v>
+      </c>
+      <c r="E133">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>6</v>
+      </c>
+      <c r="B134">
+        <v>2</v>
+      </c>
+      <c r="C134">
+        <v>3</v>
+      </c>
+      <c r="D134">
+        <v>25</v>
+      </c>
+      <c r="E134">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>6</v>
+      </c>
+      <c r="B135">
+        <v>2</v>
+      </c>
+      <c r="C135">
+        <v>4</v>
+      </c>
+      <c r="D135">
+        <v>25</v>
+      </c>
+      <c r="E135">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>6</v>
+      </c>
+      <c r="B136">
+        <v>2</v>
+      </c>
+      <c r="C136">
+        <v>5</v>
+      </c>
+      <c r="D136">
+        <v>25</v>
+      </c>
+      <c r="E136">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>6</v>
+      </c>
+      <c r="B137">
+        <v>2</v>
+      </c>
+      <c r="C137">
+        <v>1</v>
+      </c>
+      <c r="D137">
+        <v>30</v>
+      </c>
+      <c r="E137">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>6</v>
+      </c>
+      <c r="B138">
+        <v>2</v>
+      </c>
+      <c r="C138">
+        <v>2</v>
+      </c>
+      <c r="D138">
+        <v>30</v>
+      </c>
+      <c r="E138">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>6</v>
+      </c>
+      <c r="B139">
+        <v>2</v>
+      </c>
+      <c r="C139">
+        <v>3</v>
+      </c>
+      <c r="D139">
+        <v>30</v>
+      </c>
+      <c r="E139">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>6</v>
+      </c>
+      <c r="B140">
+        <v>2</v>
+      </c>
+      <c r="C140">
+        <v>4</v>
+      </c>
+      <c r="D140">
+        <v>30</v>
+      </c>
+      <c r="E140">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>6</v>
+      </c>
+      <c r="B141">
+        <v>2</v>
+      </c>
+      <c r="C141">
+        <v>5</v>
+      </c>
+      <c r="D141">
+        <v>30</v>
+      </c>
+      <c r="E141">
+        <v>0.67</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>